--- a/1_online.xlsx
+++ b/1_online.xlsx
@@ -92,7 +92,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-06 13:35</t>
+    <t>تاريخ التصدير: 2026-03-06 13:57</t>
   </si>
 </sst>
 </file>

--- a/1_online.xlsx
+++ b/1_online.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -38,6 +38,18 @@
     <t>بافلي ريمون ناجي</t>
   </si>
   <si>
+    <t>2026-03-06 19:27</t>
+  </si>
+  <si>
+    <t>01090144798</t>
+  </si>
+  <si>
+    <t>nassarareeg@gmail.com</t>
+  </si>
+  <si>
+    <t>Areeg</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -92,7 +104,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-06 13:57</t>
+    <t>تاريخ التصدير: 2026-03-07 20:15</t>
   </si>
 </sst>
 </file>
@@ -480,7 +492,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -503,67 +515,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="N4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -571,19 +583,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
         <v>8.0</v>
@@ -605,12 +617,60 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
+        <v>4.25</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="2">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H6" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2">
+        <v>4</v>
+      </c>
+      <c r="K6" s="2">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2">
+        <v>5</v>
+      </c>
+      <c r="N6" s="2">
         <v>7.3</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/1_online.xlsx
+++ b/1_online.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -50,6 +50,69 @@
     <t>Areeg</t>
   </si>
   <si>
+    <t>2026-03-09 01:38</t>
+  </si>
+  <si>
+    <t>01027005581</t>
+  </si>
+  <si>
+    <t>saramoharram90@gmail.com</t>
+  </si>
+  <si>
+    <t>Sara Hatem Moharram</t>
+  </si>
+  <si>
+    <t>2026-03-09 10:42</t>
+  </si>
+  <si>
+    <t>60.0%</t>
+  </si>
+  <si>
+    <t>01114191806</t>
+  </si>
+  <si>
+    <t>muhannad13209@gmail.com</t>
+  </si>
+  <si>
+    <t>مهند</t>
+  </si>
+  <si>
+    <t>2026-03-10 17:52</t>
+  </si>
+  <si>
+    <t>01028669301</t>
+  </si>
+  <si>
+    <t>mostafasamyk20009@gmail.com</t>
+  </si>
+  <si>
+    <t>mostafa samy</t>
+  </si>
+  <si>
+    <t>2026-03-13 12:37</t>
+  </si>
+  <si>
+    <t>01283111959</t>
+  </si>
+  <si>
+    <t>wassemjohn971@gmail.com</t>
+  </si>
+  <si>
+    <t>John Waseem Saad</t>
+  </si>
+  <si>
+    <t>2026-03-13 17:40</t>
+  </si>
+  <si>
+    <t>01002859397</t>
+  </si>
+  <si>
+    <t>arwaabdelrahman2060@icloud.com</t>
+  </si>
+  <si>
+    <t>Arwa abdelrahman abdelfattah</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -104,7 +167,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-07 20:15</t>
+    <t>تاريخ التصدير: 2026-03-14 19:05</t>
   </si>
 </sst>
 </file>
@@ -492,7 +555,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -515,67 +578,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -583,19 +646,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
         <v>8.0</v>
@@ -617,10 +680,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>4.25</v>
+        <v>9.2</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -631,46 +694,286 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J6" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
+        <v>6.93</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J7" s="2">
+        <v>4</v>
+      </c>
+      <c r="K7" s="2">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2">
+        <v>5</v>
+      </c>
+      <c r="N7" s="2">
+        <v>10.48</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="2">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="2">
+        <v>3</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2</v>
+      </c>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2">
+        <v>5</v>
+      </c>
+      <c r="N8" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="2">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J9" s="2">
+        <v>4</v>
+      </c>
+      <c r="K9" s="2">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2">
+        <v>5</v>
+      </c>
+      <c r="N9" s="2">
+        <v>8.55</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="2">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H10" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2">
+        <v>4</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2">
+        <v>5</v>
+      </c>
+      <c r="N10" s="2">
+        <v>4.25</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="2">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H11" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2">
+        <v>4</v>
+      </c>
+      <c r="K11" s="2">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2">
+        <v>5</v>
+      </c>
+      <c r="N11" s="2">
         <v>7.3</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P11" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/1_online.xlsx
+++ b/1_online.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="71">
   <si>
     <t>ناجح ✓</t>
   </si>
@@ -113,6 +113,66 @@
     <t>Arwa abdelrahman abdelfattah</t>
   </si>
   <si>
+    <t>2026-03-22 23:48</t>
+  </si>
+  <si>
+    <t>01273087315</t>
+  </si>
+  <si>
+    <t>berbarasaeid1211@gmail.com</t>
+  </si>
+  <si>
+    <t>Barbara saeid selim</t>
+  </si>
+  <si>
+    <t>2026-03-25 21:50</t>
+  </si>
+  <si>
+    <t>01122702856</t>
+  </si>
+  <si>
+    <t>jomanasayed.2008@gmail.com</t>
+  </si>
+  <si>
+    <t>Jomana Sayed Abozied</t>
+  </si>
+  <si>
+    <t>2026-03-26 20:42</t>
+  </si>
+  <si>
+    <t>01009291939</t>
+  </si>
+  <si>
+    <t>Alaaloly777@gmail.com</t>
+  </si>
+  <si>
+    <t>Alaa Mohamed Abo Soliman</t>
+  </si>
+  <si>
+    <t>2026-03-28 17:06</t>
+  </si>
+  <si>
+    <t>01127908609</t>
+  </si>
+  <si>
+    <t>arwam.hazem@gmail.com</t>
+  </si>
+  <si>
+    <t>Arwa Mohamed Hazem</t>
+  </si>
+  <si>
+    <t>2026-03-30 06:58</t>
+  </si>
+  <si>
+    <t>01040144351</t>
+  </si>
+  <si>
+    <t>Abobakrazza@gmail.com</t>
+  </si>
+  <si>
+    <t>محمد عادل حسين</t>
+  </si>
+  <si>
     <t>الحالة</t>
   </si>
   <si>
@@ -167,7 +227,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-03-14 19:05</t>
+    <t>تاريخ التصدير: 2026-04-03 13:54</t>
   </si>
 </sst>
 </file>
@@ -555,7 +615,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="true" style="0"/>
@@ -578,67 +638,67 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="3" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -646,19 +706,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
         <v>8.0</v>
@@ -680,10 +740,10 @@
         <v>5</v>
       </c>
       <c r="N5" s="2">
-        <v>9.2</v>
+        <v>5.78</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>0</v>
@@ -694,13 +754,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>3</v>
@@ -709,29 +769,29 @@
         <v>1</v>
       </c>
       <c r="G6" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H6" s="2">
         <v>10.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J6" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2">
         <v>5</v>
       </c>
       <c r="N6" s="2">
-        <v>6.93</v>
+        <v>10.15</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>0</v>
@@ -742,13 +802,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>3</v>
@@ -776,10 +836,10 @@
         <v>5</v>
       </c>
       <c r="N7" s="2">
-        <v>10.48</v>
+        <v>8.83</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>0</v>
@@ -790,13 +850,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>3</v>
@@ -805,29 +865,29 @@
         <v>2</v>
       </c>
       <c r="G8" s="2">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="H8" s="2">
         <v>10.0</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2">
         <v>5</v>
       </c>
       <c r="N8" s="2">
-        <v>1.4</v>
+        <v>3.08</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>0</v>
@@ -838,19 +898,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="2">
         <v>8.0</v>
@@ -872,10 +932,10 @@
         <v>5</v>
       </c>
       <c r="N9" s="2">
-        <v>8.55</v>
+        <v>3.52</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>0</v>
@@ -886,19 +946,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2">
         <v>8.0</v>
@@ -920,10 +980,10 @@
         <v>5</v>
       </c>
       <c r="N10" s="2">
-        <v>4.25</v>
+        <v>9.2</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>0</v>
@@ -934,46 +994,286 @@
         <v>7</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="H11" s="2">
         <v>10.0</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="J11" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2">
         <v>5</v>
       </c>
       <c r="N11" s="2">
+        <v>6.93</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H12" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="2">
+        <v>4</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2">
+        <v>5</v>
+      </c>
+      <c r="N12" s="2">
+        <v>10.48</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="2">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="H13" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" s="2">
+        <v>3</v>
+      </c>
+      <c r="K13" s="2">
+        <v>2</v>
+      </c>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2">
+        <v>5</v>
+      </c>
+      <c r="N13" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="2">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H14" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2">
+        <v>4</v>
+      </c>
+      <c r="K14" s="2">
+        <v>1</v>
+      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2">
+        <v>5</v>
+      </c>
+      <c r="N14" s="2">
+        <v>8.55</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="2">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H15" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2">
+        <v>4</v>
+      </c>
+      <c r="K15" s="2">
+        <v>1</v>
+      </c>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2">
+        <v>5</v>
+      </c>
+      <c r="N15" s="2">
+        <v>4.25</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="2">
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="H16" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2">
+        <v>4</v>
+      </c>
+      <c r="K16" s="2">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2">
+        <v>5</v>
+      </c>
+      <c r="N16" s="2">
         <v>7.3</v>
       </c>
-      <c r="O11" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="P11" s="2" t="s">
+      <c r="O16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="P16" s="2" t="s">
         <v>0</v>
       </c>
     </row>

--- a/1_online.xlsx
+++ b/1_online.xlsx
@@ -227,7 +227,7 @@
     <t>الدرجة الكاملة: 10 | درجة النجاح: 5.00</t>
   </si>
   <si>
-    <t>تاريخ التصدير: 2026-04-03 13:54</t>
+    <t>تاريخ التصدير: 2026-04-04 16:47</t>
   </si>
 </sst>
 </file>
